--- a/tests/data/fixed-template.xlsx
+++ b/tests/data/fixed-template.xlsx
@@ -447,13 +447,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Unique8983</v>
+        <v>Unique8435</v>
       </c>
       <c r="B3" t="str">
         <v>Candidate</v>
       </c>
       <c r="C3" t="str">
-        <v>+919875718913</v>
+        <v>+919866752885</v>
       </c>
       <c r="D3" t="str">
         <v>India</v>
@@ -462,7 +462,7 @@
         <v>Emirates ID</v>
       </c>
       <c r="F3" t="str">
-        <v>784-1993-3660701-6</v>
+        <v>784-1962-9028433-0</v>
       </c>
       <c r="G3" t="str">
         <v>no</v>
